--- a/database/Correspondance.xlsx
+++ b/database/Correspondance.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Q:\Commun\Generateur Etiquette\Database\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\p.bertho\Documents\generateur_etiquettes\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D00356A8-F67A-4DFC-A1B4-E349B866320A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A5CB200-BA54-47C2-A159-DA850CCD1861}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2AE81F69-3396-4D3E-A8B5-2944B23BF041}"/>
+    <workbookView xWindow="2124" yWindow="2124" windowWidth="17280" windowHeight="8880" xr2:uid="{2AE81F69-3396-4D3E-A8B5-2944B23BF041}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -195,7 +195,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -205,8 +205,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -571,7 +569,7 @@
       <c r="B2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" t="s">
         <v>17</v>
       </c>
     </row>
@@ -582,7 +580,7 @@
       <c r="B3" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" t="s">
         <v>19</v>
       </c>
     </row>
@@ -593,7 +591,7 @@
       <c r="B4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="1" t="s">
         <v>16</v>
       </c>
     </row>
@@ -604,7 +602,7 @@
       <c r="B5" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -615,7 +613,7 @@
       <c r="B6" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="5" t="s">
         <v>18</v>
       </c>
     </row>
@@ -626,7 +624,7 @@
       <c r="B7" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="5" t="s">
         <v>18</v>
       </c>
     </row>
@@ -637,7 +635,7 @@
       <c r="B8" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="5" t="s">
         <v>20</v>
       </c>
     </row>
@@ -648,7 +646,7 @@
       <c r="B9" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>22</v>
       </c>
     </row>
